--- a/Docs/B-15 Art asset list.xlsx
+++ b/Docs/B-15 Art asset list.xlsx
@@ -321,7 +321,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="2" min="2" max="2"/>
@@ -1593,7 +1593,12 @@
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Blender (wave1_weapons.py): fullered blade, crossguard, leather grip, pommel. Flat MI_Steel / MI_LeatherWrap. 538 tris.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1655,12 @@
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Turned shaft with rope grip and bands, three prongs holding a glowing orb (M_OrbGlow). 430 tris.</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1717,12 @@
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Recurve limbs, leather grip, string (M_Rope). 156 tris.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1779,12 @@
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Flanged head with gold collar and glow core (M_MaceGlow). 552 tris.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1841,12 @@
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Round buckler: iron rim, steel dome, boss, 8 gold studs, strap. 976 tris.</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1903,12 @@
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Kite shield: oak body, iron rim, blue field (MI_ShieldBlue) with an original gold chevron, boss. 300 tris.</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1965,12 @@
       </c>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Today iron_dagger reuses the sword mesh</t>
+          <t>Done 2026-09-22: New mesh; items.json iron_dagger meshId = dagger_iron. 262 tris.  (Earlier note: Today iron_dagger reuses the sword mesh)</t>
         </is>
       </c>
     </row>
@@ -1997,12 +2027,12 @@
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
-          <t>Today bone_totem reuses the mace mesh</t>
+          <t>Done 2026-09-22: New mesh (bone haft, skull knob, tusks, glowing brow gem); items.json bone_totem meshId = totem_bone. 576 tris.  (Earlier note: Today bone_totem reuses the mace mesh)</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2208,12 @@
       </c>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
         <is>
-          <t>Ground reads better as a material than as meshes</t>
+          <t>Done 2026-09-22: Flat tiles, world-aligned CC0 MI_GrassGround (ambientCG Grass004, 140 cm repeat).  (Earlier note: Ground reads better as a material than as meshes)</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2270,12 @@
       </c>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: M_ValhallaGroundBlend: dirt (Poly Haven stony_dirt_path) with a noisy grass verge by vertex colour; road lanes flipped in L_Grasslands so verges face outward (road_lanes.py).</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2332,12 @@
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: MI_StoneFloor (Poly Haven stone_tiles_02), world-aligned 136 cm. Reads a bit bright in full sun - tune BaseColor if needed.</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2394,12 @@
       </c>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr">
         <is>
-          <t>Trees are the hardest environment asset - test early</t>
+          <t>Done 2026-09-22: Procedural trunk/limbs (bark: ambientCG Bark012) + canopy clumps: opaque leaf-mass cores + masked two-sided leaf-cluster cards; leaf textures composited from ambientCG LeafSet016 (wave1_leaf_textures.py). New master M_ValhallaFoliage (Two Sided Foliage, edge-on card fade, per-tree tint variation). Old bounds kept. ~2.4k / 1.7k tris, Nanite. No wind yet.  (Earlier note: Trees are the hardest environment asset - test early)</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2456,12 @@
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Displaced + chiselled boulder, ambientCG Rock030. 662 tris.</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2518,12 @@
       </c>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Plain 64 cm slab; new master M_ValhallaWater (opaque, glossy, two panning ripple normals, fresnel colour). Ripple normal generated (wave1_water_normal.py). Pond edges still follow the tile grid.</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2580,12 @@
       </c>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
-          <t>Vision blockers: keep footprint and collision exactly</t>
+          <t>Done 2026-09-22: Rubble courses with footing and coping (MI_StoneWall = Poly Haven castle_wall_slates). Footprint / collision profile unchanged.  (Earlier note: Vision blockers: keep footprint and collision exactly)</t>
         </is>
       </c>
     </row>
@@ -2996,12 +3046,12 @@
       </c>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>Vision blockers</t>
+          <t>Done 2026-09-22: Timber frame (plinth, sill, posts, rail, brace) with recessed plaster; window with mullions and shutters; door with plank leaf and iron straps. Bounds unchanged, VisionBlocker kept.  (Earlier note: Vision blockers)</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3108,12 @@
       </c>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Thick thatch gable with ridge roll, slope-aligned UVs (Poly Haven reed_roof_04). Ridge-roll end cap UVs look stretched close up - minor.</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3170,12 @@
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>CC0 set CobbleFloor (Poly Haven cobblestone_floor_001) already imported in Wave 0; world-aligned at 160 cm per repeat.</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L48" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: MI_CobbleFloor world-aligned 160 cm (Wave 0 set) applied.</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3232,12 @@
       </c>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: MI_WoodPlanks (Poly Haven old_wood_floor) world-aligned 204 cm.</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3294,12 @@
       </c>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
-          <t>Keep footprint (Bjorn stands at it)</t>
+          <t>Done 2026-09-22: Posts, counter, striped awning (MI_CanvasRed / MI_CanvasCream), goods. Footprint kept. 7 material slots (over the 3-slot guide; fine with Nanite, trim sheet later).  (Earlier note: Keep footprint (Bjorn stands at it))</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3356,12 @@
       </c>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Stone ring, roof on posts, windlass, rope and bucket. 7 slots (see A-049).</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3418,12 @@
       </c>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Iron post and lantern (emissive MI_LanternGlass) + a real warm PointLight per lamp (lamp_lights.py, no shadows).</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3480,12 @@
       </c>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Picket fence, MI_FenceWood.</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3542,12 @@
       </c>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Post and arrow boards.</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3604,12 @@
       </c>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Staves and iron hoops (lathe).</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3666,12 @@
       </c>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Plank crate with corner braces.</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3728,12 @@
       </c>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
-          <t>Keep the click sphere</t>
+          <t>Done 2026-09-22: Burlap sack with rope tie (MI_Burlap). Click sphere / collision profile kept.  (Earlier note: Keep the click sphere)</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4150,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L64" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: lighting_remaster.py LOOK applied to L_World - warm late-afternoon sun, Lumen sky fill + faint cool fill, haze from 1800 cm, gentle grade. Outline retired (valhalla.Visual.Outline 1 restores it). Removed the stray DirectionalLights in L_Grasslands and L_Desert (double shadows).</t>
         </is>
@@ -5246,7 +5336,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" s="2">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>A-084</t>
@@ -5305,6 +5395,192 @@
       <c r="L85" s="1" t="inlineStr">
         <is>
           <t>Blender assets/scripts/valhalla_textures.py exports T_&lt;Set&gt;_BC / _N (DirectX) / _ORM; valhalla_tools/import_texture_sets.py imports and builds MI_&lt;Set&gt; on M_ValhallaPBR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" s="2">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>A-085</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>M_ValhallaGroundBlend</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>Road tiles</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>Unreal Python (build_pbr.build_ground_blend)</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>CC0 sets</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="K86" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L86" s="1" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Two world-aligned layers blended by vertex colour R with noise-broken edge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" s="2">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>A-086</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>M_ValhallaFoliage</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>Trees (and later bushes)</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>Unreal Python (build_pbr.build_foliage)</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>CC0 leaf composites</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>Optional wind (WPO) later</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="K87" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L87" s="1" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Masked, two-sided, Two Sided Foliage; BaseColor alpha = mask; EdgeFade for cards; per-tree tint from PerInstanceRandom + object-position hash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" s="2">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>A-087</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>M_ValhallaWater</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>SM_Water</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>Unreal Python (build_pbr.build_water)</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>Generated ripple normal</t>
+        </is>
+      </c>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="inlineStr">
+        <is>
+          <t>Wave 1</t>
+        </is>
+      </c>
+      <c r="K88" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L88" s="1" t="inlineStr">
+        <is>
+          <t>Done 2026-09-22: Opaque glossy water, two panning normals, fresnel deep/edge colour.</t>
         </is>
       </c>
     </row>

--- a/Docs/B-15 Art asset list.xlsx
+++ b/Docs/B-15 Art asset list.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Keep skeleton and bone names so equipment and animations still fit; leave room for race proportions (shape keys / bone scale)</t>
+          <t>Done 2026-09-23 (Fable 5.1): Organic body: parametric shells -&gt; voxel remesh -&gt; scripted sculpt -&gt; QuadriFlow retopo (wave2_body.py), scripted weights on the unchanged skeleton (same 24 joints, sockets). 8,844 tris. Procedural skin set SkinBase (baked, own work); runtime BaseColor tint still works. Race_Stocky/Slender shape keys in .blend/glb only.</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,12 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Clumped hair cards on the new cranium, vertex-colour roots (wave2_hair.py). 5,022 tris. HairStrands procedural set.</t>
         </is>
       </c>
     </row>
@@ -562,7 +567,12 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Short clumped hair with fringe. 4,590 tris.</t>
         </is>
       </c>
     </row>
@@ -619,7 +629,12 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Scalp patch on skin material. 972 tris.</t>
         </is>
       </c>
     </row>
@@ -676,12 +691,12 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Keep asset name (meshId/spriteId mapping)</t>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather jerkin with straps, studs, belt. 1,252 tris. ambientCG Leather028.</t>
         </is>
       </c>
     </row>
@@ -738,7 +753,12 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Chain shirt (ambientCG Chainmail004) with cloth tabard. 1,712 tris.</t>
         </is>
       </c>
     </row>
@@ -795,7 +815,12 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Blue robe, bell sleeves, rope belt (ambientCG Fabric032 tinted). 2,488 tris.</t>
         </is>
       </c>
     </row>
@@ -852,7 +877,12 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth trousers with leather patches. 1,784 tris.</t>
         </is>
       </c>
     </row>
@@ -909,7 +939,12 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate cuisses/greaves with knee cops (ambientCG Metal009). 1,704 tris.</t>
         </is>
       </c>
     </row>
@@ -966,7 +1001,12 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Robe skirt (stretches between legs rather than swinging). 1,008 tris.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1063,12 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather boots. 1,576 tris.</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1125,12 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate sabatons. 1,528 tris.</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1187,12 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth slippers. 856 tris.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1249,12 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather bracers. 1,568 tris.</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1311,12 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Gauntlets with knuckle lames. 1,424 tris.</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1373,12 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth wraps (stacked bands). 1,696 tris.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1435,12 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Full helm, T-visor, crest. 960 tris.</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1497,12 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather hood with mantle (stiff). 1,140 tris.</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1559,12 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wizard hat with bent cone. 868 tris.</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1621,12 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wool cloak (stiff sheet, no cloth sim). 664 tris.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1686,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Blender (wave1_weapons.py): fullered blade, crossguard, leather grip, pommel. Flat MI_Steel / MI_LeatherWrap. 538 tris.</t>
         </is>
@@ -1658,7 +1748,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Turned shaft with rope grip and bands, three prongs holding a glowing orb (M_OrbGlow). 430 tris.</t>
         </is>
@@ -1720,7 +1810,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Recurve limbs, leather grip, string (M_Rope). 156 tris.</t>
         </is>
@@ -1782,7 +1872,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Flanged head with gold collar and glow core (M_MaceGlow). 552 tris.</t>
         </is>
@@ -1844,7 +1934,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Round buckler: iron rim, steel dome, boss, 8 gold studs, strap. 976 tris.</t>
         </is>
@@ -1906,7 +1996,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Kite shield: oak body, iron rim, blue field (MI_ShieldBlue) with an original gold chevron, boss. 300 tris.</t>
         </is>
@@ -2089,12 +2179,12 @@
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
-          <t>Quality check each cycle in Play; animation is the hardest category</t>
+          <t>Done 2026-09-23 (Fable 5.1): Re-keyed by wave2_anims.py (FK + planted-foot leg solver), same names, 30 fps: Idle 2.0 s loop, Walk 0.667 s loop (matches 122 cm/s), Attack/Shoot 0.667 s, Cast 0.8 s, Hit 0.4 s, Death 1.2 s hold. No gameplay timing depends on length.</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2241,12 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2368,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: M_ValhallaGroundBlend: dirt (Poly Haven stony_dirt_path) with a noisy grass verge by vertex colour; road lanes flipped in L_Grasslands so verges face outward (road_lanes.py).</t>
         </is>
@@ -2335,7 +2430,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: MI_StoneFloor (Poly Haven stone_tiles_02), world-aligned 136 cm. Reads a bit bright in full sun - tune BaseColor if needed.</t>
         </is>
@@ -2459,7 +2554,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Displaced + chiselled boulder, ambientCG Rock030. 662 tris.</t>
         </is>
@@ -2521,7 +2616,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Plain 64 cm slab; new master M_ValhallaWater (opaque, glossy, two panning ripple normals, fresnel colour). Ripple normal generated (wave1_water_normal.py). Pond edges still follow the tile grid.</t>
         </is>
@@ -3111,7 +3206,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Thick thatch gable with ridge roll, slope-aligned UVs (Poly Haven reed_roof_04). Ridge-roll end cap UVs look stretched close up - minor.</t>
         </is>
@@ -3235,7 +3330,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="L49" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: MI_WoodPlanks (Poly Haven old_wood_floor) world-aligned 204 cm.</t>
         </is>
@@ -3359,7 +3454,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L51" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Stone ring, roof on posts, windlass, rope and bucket. 7 slots (see A-049).</t>
         </is>
@@ -3421,7 +3516,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L52" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Iron post and lantern (emissive MI_LanternGlass) + a real warm PointLight per lamp (lamp_lights.py, no shadows).</t>
         </is>
@@ -3483,7 +3578,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Picket fence, MI_FenceWood.</t>
         </is>
@@ -3545,7 +3640,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L54" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Post and arrow boards.</t>
         </is>
@@ -3607,7 +3702,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L55" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Staves and iron hoops (lathe).</t>
         </is>
@@ -3669,7 +3764,7 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L56" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Plank crate with corner braces.</t>
         </is>

--- a/Docs/B-15 Art asset list.xlsx
+++ b/Docs/B-15 Art asset list.xlsx
@@ -321,7 +321,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="2" min="2" max="2"/>
@@ -398,7 +398,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>SK_Valhalla_Body</t>
+          <t>SKM_MHC_ValhallaBase (MetaHuman body + face)</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -413,7 +413,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Existing (replaced)</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -423,17 +423,17 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: organic body (base mesh for all humanoid races)</t>
+          <t>MetaHuman Creator in UE 5.8 (MetaHumanCharacter plugin), Optimized / Medium build</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>CC0 skin/cloth textures or procedural bake</t>
+          <t>MetaHuman skin (baked by the build)</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>Rig on SK_Valhalla_Skeleton; weights hand-tuned</t>
+          <t>metahuman_base_skel; face mesh follows the body by leader pose</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
@@ -448,7 +448,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Done 2026-09-23 (Fable 5.1): Organic body: parametric shells -&gt; voxel remesh -&gt; scripted sculpt -&gt; QuadriFlow retopo (wave2_body.py), scripted weights on the unchanged skeleton (same 24 joints, sockets). 8,844 tris. Procedural skin set SkinBase (baked, own work); runtime BaseColor tint still works. Race_Stocky/Slender shape keys in .blend/glb only.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Replaced the Fable 5.1 organic body with the MetaHuman base MHC_ValhallaBase, nude in underwear, drawn at 122/180.3 scale, facing +Y. Content in /Game/Valhalla/Characters/MetaHuman/ (~455 MB with Build + Export). The Fable body remains as valhalla.Visual.BodyProfile 0. The Paragon Gideon trial body was archived outside the repo (Valhalla-archive/ParagonGideon_2026-09-23). Armour and hair must be rebuilt on metahuman_base_skel (A-002..A-020).</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Clumped hair cards on the new cranium, vertex-colour roots (wave2_hair.py). 5,022 tris. HairStrands procedural set.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Clumped hair cards on the new cranium, vertex-colour roots (wave2_hair.py). 5,022 tris. HairStrands procedural set.</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Short clumped hair with fringe. 4,590 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Short clumped hair with fringe. 4,590 tris.</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Scalp patch on skin material. 972 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L5" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Scalp patch on skin material. 972 tris.</t>
         </is>
       </c>
     </row>
@@ -691,12 +691,12 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather jerkin with straps, studs, belt. 1,252 tris. ambientCG Leather028.</t>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather jerkin with straps, studs, belt. 1,252 tris. ambientCG Leather028.</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Chain shirt (ambientCG Chainmail004) with cloth tabard. 1,712 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L7" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Chain shirt (ambientCG Chainmail004) with cloth tabard. 1,712 tris.</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Blue robe, bell sleeves, rope belt (ambientCG Fabric032 tinted). 2,488 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L8" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Blue robe, bell sleeves, rope belt (ambientCG Fabric032 tinted). 2,488 tris.</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth trousers with leather patches. 1,784 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L9" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth trousers with leather patches. 1,784 tris.</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate cuisses/greaves with knee cops (ambientCG Metal009). 1,704 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L10" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate cuisses/greaves with knee cops (ambientCG Metal009). 1,704 tris.</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Robe skirt (stretches between legs rather than swinging). 1,008 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L11" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Robe skirt (stretches between legs rather than swinging). 1,008 tris.</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather boots. 1,576 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L12" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather boots. 1,576 tris.</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate sabatons. 1,528 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L13" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate sabatons. 1,528 tris.</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth slippers. 856 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L14" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth slippers. 856 tris.</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather bracers. 1,568 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L15" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather bracers. 1,568 tris.</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Gauntlets with knuckle lames. 1,424 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L16" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Gauntlets with knuckle lames. 1,424 tris.</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth wraps (stacked bands). 1,696 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L17" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth wraps (stacked bands). 1,696 tris.</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Full helm, T-visor, crest. 960 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L18" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Full helm, T-visor, crest. 960 tris.</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather hood with mantle (stiff). 1,140 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L19" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather hood with mantle (stiff). 1,140 tris.</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wizard hat with bent cone. 868 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L20" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wizard hat with bent cone. 868 tris.</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wool cloak (stiff sheet, no cloth sim). 664 tris.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L21" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wool cloak (stiff sheet, no cloth sim). 664 tris.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Animations (7): Idle Walk Attack Shoot Cast Hit Death</t>
+          <t>Animations: Idle Walk Jog Attack Hit Death (MetaHuman)</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Existing</t>
+          <t>Existing (replaced)</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: scripted keyframe animation on SK_Valhalla_Skeleton</t>
+          <t>Retargeted from the UE5 Mannequin (IK_Manny -&gt; IK_MH_ValhallaBase) + hand-keyed fixes (Tools/anim_authoring)</t>
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr">
@@ -2184,11 +2184,11 @@
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
-          <t>Done 2026-09-23 (Fable 5.1): Re-keyed by wave2_anims.py (FK + planted-foot leg solver), same names, 30 fps: Idle 2.0 s loop, Walk 0.667 s loop (matches 122 cm/s), Attack/Shoot 0.667 s, Cast 0.8 s, Hit 0.4 s, Death 1.2 s hold. No gameplay timing depends on length.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t>Done 2026-09-23 (Opus 5.5): MetaHuman set in /Game/Valhalla/Characters/MetaHuman/Animations. Idle MH_MM_Idle re-posed relaxed (arms at the sides, hands at rest). Walk MH_MF_Unarmed_Walk_Fwd and Jog MH_MF_Unarmed_Jog_Fwd, play rate matched to speed. Unarmed attack MH_MM_Attack_01. Hit MH_MM_HitReact_Front_Lgt_01 on an additive layer (fixed the combat flicker). Death MH_MM_Death_Front_01. Shoot and Cast moved to A-088/A-091. Mannequin source archived (Valhalla-archive/UE5Mannequins_2026-09-23). Fable 5.1 clips kept for BodyProfile 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" s="2">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>A-030</t>
@@ -2241,12 +2241,12 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="L31" s="0" t="inlineStr">
+        <is>
+          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the clips below are on SK_Valhalla_Skeleton; MetaHuman versions are hand-keyed in Tools/anim_authoring. Still not wired into gameplay. | Previous: Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
         </is>
       </c>
     </row>
@@ -5676,6 +5676,316 @@
       <c r="L88" s="1" t="inlineStr">
         <is>
           <t>Done 2026-09-22: Opaque glossy water, two panning normals, fresnel deep/edge colour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" s="2">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>A-088</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>Weapon attacks (MetaHuman): MH_Attack_Sword / _Dagger / _Mace / _Staff / _Bow</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Animation</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>Auto-attack with a weapon (AttackAnimForWeapon, by weaponStyle)</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>Hand-keyed in Python (Tools/anim_authoring/author.py)</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K89" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): One swing per weapon style: sword slash, dagger thrust, mace overhead, staff two-hand strike, bow draw-and-loose (Shoot). Unarmed stays MH_MM_Attack_01. items.json iron_dagger weaponStyle = dagger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" s="2">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>A-089</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>Stance poses: MHP_GripR / MHP_GripL / MHP_ShieldArm</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Animation</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>Any character holding a weapon or shield</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>Hand-keyed; layered per branch in ValhallaAnimInstance (HandLayer)</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K90" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): Fingers close on the weapon in the right hand (or the left for a bow), and the forearm comes up to carry a shield. Blended over idle, walk and attacks. Grip transforms for sword, staff, bow and shield are in ValhallaVisuals GripFrame (Tools/anim_authoring grips).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" s="2">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>A-090</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>Bow skill hold: MH_Bow_Draw / MH_Bow_Release</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>Animation</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>Skills with castAnimation "bow" (ranger_aimed_shot)</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>Hand-keyed (author.py)</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K91" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): Draws the bow and holds at full draw for the cast time, then looses when the cast completes. Skill field castAnimation (skills.json, editor checkbox "Bow Draw While Casting"). Candidates for later: Snipe, Multi-Shot, Serpent Arrow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" s="2">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>A-091</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>Casts: MH_Cast_Instant(_Staff), MH_Cast_Channel(_Staff), MH_Cast_Release(_Staff)</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Animation</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>Every spell</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>Hand-keyed (author.py)</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): Replaced the Gideon cast. Open-hand and staff variants: a looping channel while the cast bar runs, a release when it completes, and an instant cast for spells with no cast time. Works with a mace + buckler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" s="2">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>A-092</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>MetaHuman retarget + authoring tools (IK_MH_ValhallaBase, Tools/anim_authoring)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>Animation pipeline</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
+          <t>IK Rig / IK Retargeter from Python; FK keyframe authoring</t>
+        </is>
+      </c>
+      <c r="J93" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K93" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): Tools/anim_authoring: skeleton maths, rig, keyframe engine (Catmull-Rom), UE read/write of AnimSequences, retarget script. IK_MH_ValhallaBase is the target rig; run_op_initial_setup is required on every op or the pelvis lands at 0.</t>
         </is>
       </c>
     </row>

--- a/Docs/B-15 Art asset list.xlsx
+++ b/Docs/B-15 Art asset list.xlsx
@@ -321,7 +321,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="42.25" customWidth="1" style="2" min="2" max="2"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: hair cards/mesh</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J3" s="1" t="inlineStr">
@@ -505,12 +505,12 @@
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L3" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Clumped hair cards on the new cranium, vertex-colour roots (wave2_hair.py). 5,022 tris. HairStrands procedural set.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Same, shoulder-length strands pick up neck and spine weights. 5,022 tris. /Game/Valhalla/Characters/MetaHuman/Hair/SK_Hair_Blonde; source Import/Characters/MetaHuman/Hair/SK_Hair_Blonde.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Hair for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Clumped hair cards on the new cranium, vertex-colour roots (wave2_hair.py). 5,022 tris. HairStrands procedural set.</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: hair cards/mesh</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L4" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Short clumped hair with fringe. 4,590 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. wave2_hair designs on the MetaHuman cranium (wave2mh_hair.py), pushed clear of the skin, head weights. Vertex colour exported linear. 4,320 tris. /Game/Valhalla/Characters/MetaHuman/Hair/SK_Hair_Brown_Short; source Import/Characters/MetaHuman/Hair/SK_Hair_Brown_Short.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Hair for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Short clumped hair with fringe. 4,590 tris.</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not needed</t>
         </is>
       </c>
       <c r="L5" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Scalp patch on skin material. 972 tris.</t>
+          <t>Not needed on the MetaHuman (2026-09-23 (Opus 5.5)): the cap was the scalp a hood sat on over the Fable skull; the MetaHuman head is its own scalp, and nothing in code or data references it. The Fable version stays for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Scalp patch on skin material. 972 tris.</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
@@ -691,12 +691,12 @@
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather jerkin with straps, studs, belt. 1,252 tris. ambientCG Leather028.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Torso rings up to the neck, shoulder caps on the MetaHuman arm line, belt, straps and studs. 1,460 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_chest_travelers_jerkin; source Import/Characters/MetaHuman/Equipment/SK_chest_travelers_jerkin.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather jerkin with straps, studs, belt. 1,252 tris. ambientCG Leather028.</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L7" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Chain shirt (ambientCG Chainmail004) with cloth tabard. 1,712 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Mail shirt and sleeves. Tabard panels draped over the body's outer envelope (so they clear the belly), with a leather hem. 2,104 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_chest_priests_chain; source Import/Characters/MetaHuman/Equipment/SK_chest_priests_chain.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Chain shirt (ambientCG Chainmail004) with cloth tabard. 1,712 tris.</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L8" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Blue robe, bell sleeves, rope belt (ambientCG Fabric032 tinted). 2,488 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Robe body and bell sleeves. Skirt draped to the knee over hips and thighs, cream hem, rope belt, cowl. 2,888 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_chest_apprentice_robe; source Import/Characters/MetaHuman/Equipment/SK_chest_apprentice_robe.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Blue robe, bell sleeves, rope belt (ambientCG Fabric032 tinted). 2,488 tris.</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L9" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth trousers with leather patches. 1,784 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Seat and hips as a shell of the body (rings cannot cover the crotch), trouser legs, knee patches, belt. 1,986 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_legs_travelers; source Import/Characters/MetaHuman/Equipment/SK_legs_travelers.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth trousers with leather patches. 1,784 tris.</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L10" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate cuisses/greaves with knee cops (ambientCG Metal009). 1,704 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Leather breeches shell under a fauld, cuisses, knee cops and greaves. 2,272 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_legs_iron_plate; source Import/Characters/MetaHuman/Equipment/SK_legs_iron_plate.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate cuisses/greaves with knee cops (ambientCG Metal009). 1,704 tris.</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L11" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Robe skirt (stretches between legs rather than swinging). 1,008 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Waist band and a skirt draped to the ankle, cream hem. 1,176 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_legs_apprentice_robe; source Import/Characters/MetaHuman/Equipment/SK_legs_apprentice_robe.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Robe skirt (stretches between legs rather than swinging). 1,008 tris.</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L12" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather boots. 1,576 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. The foot is a shell of the MetaHuman's own foot (toes and all), plus shaft, cuff, instep strap and sole. 2,410 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_boots_ranger; source Import/Characters/MetaHuman/Equipment/SK_boots_ranger.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather boots. 1,576 tris.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L13" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate sabatons. 1,528 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Foot shell in plate, three lames, ankle greave, sole. 2,361 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_boots_iron_sabatons; source Import/Characters/MetaHuman/Equipment/SK_boots_iron_sabatons.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Plate sabatons. 1,528 tris.</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L14" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth slippers. 856 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Foot shell in cloth, ankle tie, thin sole. 1,689 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_boots_cloth_slippers; source Import/Characters/MetaHuman/Equipment/SK_boots_cloth_slippers.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth slippers. 856 tris.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L15" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather bracers. 1,568 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. The hand is a shell of the MetaHuman's own hand (five fingers, deforms with the grips). Leather bracers with straps. 2,834 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_gloves_ranger_bracers; source Import/Characters/MetaHuman/Equipment/SK_gloves_ranger_bracers.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather bracers. 1,568 tris.</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L16" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Gauntlets with knuckle lames. 1,424 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Plate hand shell, flared cuff. The Fable knuckle lames were dropped: a band cannot sit on the posed MetaHuman hand. 2,449 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_gloves_iron_gauntlets; source Import/Characters/MetaHuman/Equipment/SK_gloves_iron_gauntlets.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Gauntlets with knuckle lames. 1,424 tris.</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L17" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth wraps (stacked bands). 1,696 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Cloth hand shell and wrapped forearm bands. 2,960 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_gloves_cloth_wraps; source Import/Characters/MetaHuman/Equipment/SK_gloves_cloth_wraps.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Cloth wraps (stacked bands). 1,696 tris.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L18" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Full helm, T-visor, crest. 960 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Neck guard, face opening and skull on the MetaHuman head, nasal and brow bars, crest. Rigid on the head bone. 1,016 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_helm_iron_full; source Import/Characters/MetaHuman/Equipment/SK_helm_iron_full.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Full helm, T-visor, crest. 960 tris.</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L19" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather hood with mantle (stiff). 1,140 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Hood on the head bone. Leather mantle fitted over the shoulders; it keeps its arm weights so it follows the arms down from the A-pose. 1,324 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_hood_scout; source Import/Characters/MetaHuman/Equipment/SK_hood_scout.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Leather hood with mantle (stiff). 1,140 tris.</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L20" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wizard hat with bent cone. 868 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Brim at the brow, crown, bent cone. Rigid on the head bone. 868 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_hat_adept; source Import/Characters/MetaHuman/Equipment/SK_hat_adept.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wizard hat with bent cone. 868 tris.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>Opus 5.5 + Blender MCP: model fitted to body</t>
+          <t>Opus 5.5 + Blender MCP: re-fitted to the MetaHuman by script (wave2mh_armour.py / wave2mh_hair.py)</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Weight transfer from body (cloth sim optional)</t>
+          <t>Weights transferred from the MetaHuman body/face (metahuman_base_skel), max 6 influences</t>
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L21" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the version below is skinned to SK_Valhalla_Skeleton, cannot follow metahuman_base_skel and is hidden on the MetaHuman body. | Previous: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wool cloak (stiff sheet, no cloth sim). 664 tris.</t>
+          <t>Done 2026-09-23 (Opus 5.5): Rebuilt for the MetaHuman body. Shoulder cape that follows the arms. Back panel draped to the calf with smoothed spine weights, leather hem, clasp. 888 tris. /Game/Valhalla/Characters/MetaHuman/Equipment/SK_cloak_warden; source Import/Characters/MetaHuman/Equipment/SK_cloak_warden.fbx, Blender assets/Characters/valhalla_mh_equipment.blend. The Fable 5.1 version stays in Characters/Equipment for BodyProfile 0. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Built by wave2_armour.py: ray-cast fitted to the new body, skinned with the body weights, Race_Stocky/Slender keys (not imported: morph targets off). Wool cloak (stiff sheet, no cloth sim). 664 tris.</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Animations: Run Sit Emotes 2H-attack Block Dodge</t>
+          <t>Animations: Run Sit Emotes 2H-attack Block Dodge (MetaHuman)</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: scripted keyframe animation</t>
+          <t>Hand-keyed (Tools/anim_authoring/author_extra.py): pelvis and planted-foot leg IK added to the author.py engine</t>
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L31" s="0" t="inlineStr">
         <is>
-          <t>Rework for the MetaHuman body in progress (2026-09-23 (Opus 5.5)): the clips below are on SK_Valhalla_Skeleton; MetaHuman versions are hand-keyed in Tools/anim_authoring. Still not wired into gameplay. | Previous: Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
+          <t>Done 2026-09-23 (Opus 5.5): MH_Sit (0.8 s down to the ground, holds the last frame), MH_Emote_Wave, MH_Emote_Cheer, MH_Emote_Bow, MH_Attack_2H (two-handed overhead chop, left hand on the grip below the right), MH_Block (shield raised to the face, weapon across; the forearm is rolled so the shield faces forward), MH_Dodge (in-place sidestep). Run = MH_MF_Unarmed_Jog_Fwd, already the jog in locomotion. Still NOT wired into gameplay: needs EValhallaAnim entries, /sit and emote commands, a TwoHand weapon style, and Block/Dodge on combat events. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="L82" s="1" t="inlineStr">
         <is>
-          <t>Planned; all characters are human for now. A-001 is designed to allow it</t>
+          <t>Planned; all characters are human for now. A-001 is designed to allow it | 2026-09-23: on the MetaHuman a race would be another MetaHuman Creator build on metahuman_base_skel; wave2mh_armour/hair re-fit to any body prep() is pointed at.</t>
         </is>
       </c>
     </row>
@@ -5986,6 +5986,68 @@
       <c r="L93" s="0" t="inlineStr">
         <is>
           <t>Done 2026-09-23 (Opus 5.5): Tools/anim_authoring: skeleton maths, rig, keyframe engine (Catmull-Rom), UE read/write of AnimSequences, retarget script. IK_MH_ValhallaBase is the target rig; run_op_initial_setup is required on every op or the pelvis lands at 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" s="2">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>A-093</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>MetaHuman fitting pipeline (wave2mh_base.py, mh_fbx_export.py, mh_equipment_import.py)</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>Tooling</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>Armour and hair for the MetaHuman body</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>Weight transfer from the MetaHuman; FBX round trip onto metahuman_base_skel</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="inlineStr">
+        <is>
+          <t>Wave 2</t>
+        </is>
+      </c>
+      <c r="K94" s="1" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L94" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-23 (Opus 5.5): Unreal exports the body and face to Import/Characters/MetaHuman/MH_*.fbx. wave2mh_base.prep() rebuilds them in Blender as the fitting reference and maps Fable landmark heights onto the MetaHuman (Z) and offsets x 180.3/122 (O). drape() hangs cloth over the outer envelope; skin_shell() copies the body's own skin for hands, feet and hips; transfer_weights() takes the MetaHuman's weights. Saved/ClaudeOps/mh_equipment_import.py imports onto metahuman_base_skel and binds MI_ slots by name. The reference pose was checked bone by bone against the body (every skinned bone matches). ValhallaVisuals: SkinnedArtRoot / EquipmentMeshPath / HairMeshPath, and PieceForActiveBody swaps an NPC's Fable piece for its MetaHuman rebuild.</t>
         </is>
       </c>
     </row>

--- a/Docs/B-15 Art asset list.xlsx
+++ b/Docs/B-15 Art asset list.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>Done 2026-09-23 (Opus 5.5): Replaced the Fable 5.1 organic body with the MetaHuman base MHC_ValhallaBase, nude in underwear, drawn at 122/180.3 scale, facing +Y. Content in /Game/Valhalla/Characters/MetaHuman/ (~455 MB with Build + Export). The Fable body remains as valhalla.Visual.BodyProfile 0. The Paragon Gideon trial body was archived outside the repo (Valhalla-archive/ParagonGideon_2026-09-23). Armour and hair must be rebuilt on metahuman_base_skel (A-002..A-020).</t>
+          <t>Done 2026-09-23 (Opus 5.5): Replaced the Fable 5.1 organic body with the MetaHuman base MHC_ValhallaBase, nude in underwear, drawn at 122/180.3 scale, facing +Y. Content in /Game/Valhalla/Characters/MetaHuman/ (~455 MB with Build + Export). The Fable body remains as valhalla.Visual.BodyProfile 0. The Paragon Gideon trial body was archived outside the repo (Valhalla-archive/ParagonGideon_2026-09-23). Armour and hair were rebuilt on metahuman_base_skel (A-002..A-020).</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L31" s="0" t="inlineStr">
         <is>
-          <t>Done 2026-09-23 (Opus 5.5): MH_Sit (0.8 s down to the ground, holds the last frame), MH_Emote_Wave, MH_Emote_Cheer, MH_Emote_Bow, MH_Attack_2H (two-handed overhead chop, left hand on the grip below the right), MH_Block (shield raised to the face, weapon across; the forearm is rolled so the shield faces forward), MH_Dodge (in-place sidestep). Run = MH_MF_Unarmed_Jog_Fwd, already the jog in locomotion. Still NOT wired into gameplay: needs EValhallaAnim entries, /sit and emote commands, a TwoHand weapon style, and Block/Dodge on combat events. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
+          <t>Done 2026-09-23 (Opus 5.5): MH_Sit (0.8 s down to the ground, holds the last frame), MH_Emote_Wave, MH_Emote_Cheer, MH_Emote_Bow, MH_Attack_2H (two-handed overhead chop, left hand on the grip below the right), MH_Block (shield raised to the face, weapon across; the forearm is rolled so the shield faces forward), MH_Dodge (in-place sidestep). Run = MH_MF_Unarmed_Jog_Fwd, already the jog in locomotion. Wired 2026-09-23: chat /sit (toggles) /stand /wave /cheer /bow (ServerEmote; sitting replicates, emotes multicast; moving, casting, attacking or dying stands you up); A_Block / A_Dodge play on the defender of a blocked / dodged blow (not over a swing); weaponStyle "greatsword" uses MH_Attack_2H and is two-handed. Sitting regen and Meditate: backlog B-18. | Fable 5.1: Done 2026-09-23 (Fable 5.1): Authored and imported (A_Run, A_Sit, A_Emote_Wave/Cheer/Bow, A_Attack2H, A_Block, A_Dodge); added to character_import.ANIMATIONS. NOT wired into gameplay yet - needs EValhallaAnim entries, run locomotion blend, /sit &amp; emote commands, TwoHand attack cycle, Block/Dodge on combat events.</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2717,12 @@
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>Ground surface</t>
+          <t>Opus 5.5 + Blender MCP: 64 cm tiles, 7.3 cm top as the first pass</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>CC0 tiling material</t>
+          <t>CC0: ambientCG Ground080 (DesertSand) + Ground097 (SandRipples)</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr">
@@ -2737,7 +2737,12 @@
       </c>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L39" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): MI_SandBlend on M_ValhallaGroundBlend: DesertSand, with patches of wind-rippled SandRipples painted by vertex colour on B and C (faded out at every tile edge, so any tile meets any other). World-aligned, 200 / 150 cm. Tint 0.74/0.69/0.62.</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2779,12 @@
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural terrain</t>
+          <t>Opus 5.5 + Blender MCP: procedural mound</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>CC0 sand</t>
+          <t>CC0 sand (MI_SandBlend)</t>
         </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
@@ -2794,7 +2799,12 @@
       </c>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L40" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): In the Desert every dune is its own actor on top of a sand tile (scaled 1.1-1.6, diagonal chains), so the square first-pass tile showed as a raised square. Now only the mound: round, 0.96 m across (neighbours overlap into bumpy ridges along either diagonal), gentle windward side and steep slip face, rim 2 cm up so it rises out of the sand with no edge. Ripples on the upper windward slope.</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2841,12 @@
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>Ground surface</t>
+          <t>Opus 5.5 + Blender MCP: 64 cm tile, 6.2 cm top</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>CC0 tiling material</t>
+          <t>CC0: Poly Haven dry_ground_01 (CrackedEarth)</t>
         </is>
       </c>
       <c r="I41" s="1" t="inlineStr">
@@ -2851,7 +2861,12 @@
       </c>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): MI_CrackedBlend: cracked clay pan in the middle, drifted sand creeping in at the edges (half and half at the very edge, so a cluster of pans reads as one). Warmer tint than the grey scan.</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2903,12 @@
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: organic model</t>
+          <t>Opus 5.5 + Blender MCP: fluted stems (ribbed lathe along a path)</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>Procedural / CC0</t>
+          <t>Procedural rib texture (wave3_cactus_texture.py): areoles and spines on each rib crest</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
@@ -2908,7 +2923,12 @@
       </c>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): A: saguaro-like column with two elbowed arms, 10 ribs. B: barrel cactus with a pup and three flowers (MI_CactusFlower). One texture repeat per rib across and per metre up. First-pass bounds kept.</t>
         </is>
       </c>
     </row>
@@ -2945,12 +2965,12 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural tree + frond cards</t>
+          <t>Opus 5.5 + Blender MCP: ringed leaning trunk + 13 frond cards</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>CC0 bark + leaf atlas</t>
+          <t>CC0: Poly Haven palm_bark; frond texture procedural (wave3_palm_texture.py)</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -2965,7 +2985,12 @@
       </c>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): Trunk with leaf-scar rings and flared foot (MI_PalmBark), crown boot, hanging fruit (MI_Coconut), 9 drooping + 4 rising fronds folded along the rachis; MI_PalmFrond on M_ValhallaFoliage (masked, two-sided). ~1.2k tris. Wind not done.</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3027,12 @@
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural rock</t>
+          <t>Opus 5.5 + Blender MCP: procedural rock</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>CC0 sandstone</t>
+          <t>CC0: Poly Haven old_sandstone_02 (SandstoneRock)</t>
         </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
@@ -3022,7 +3047,12 @@
       </c>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L44" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): Wind-carved sandstone boulder: bedding planes eroded into ledges, undercut foot, flattened top; strata run horizontal. First-pass bounds kept.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3089,12 @@
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural modular</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>CC0 sandstone</t>
+          <t>CC0: Poly Haven sandstone_blocks_05 (SandstoneBlocks)</t>
         </is>
       </c>
       <c r="I45" s="1" t="inlineStr">
@@ -3079,12 +3109,12 @@
       </c>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
         <is>
-          <t>Vision blockers</t>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): Dressed ashlar: projecting plinth, body, string course and individual capstones (a few worn lower); the end pier has a moulded cap and a low pyramid stone. Bounds identical to the first pass; VisionBlocker kept. Block joints do not line up across module seams (box UVs per module); not noticeable from the game camera.  (Earlier note: Vision blockers)</t>
         </is>
       </c>
     </row>
@@ -3865,12 +3895,12 @@
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: model + VFX</t>
+          <t>Opus 5.5 + Blender MCP: model</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>Procedural</t>
+          <t>MI_StoneWall plinth, MI_Rock obelisk, M_PortalGlow runes</t>
         </is>
       </c>
       <c r="I58" s="1" t="inlineStr">
@@ -3885,7 +3915,12 @@
       </c>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L58" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave3_desert.py): Rune-stone: two-step octagonal plinth with a glowing ring inlay, tapering obelisk with a pyramidion and glowing rune bars on four faces. Same 1.21 m height, slightly smaller footprint; collision profile kept. M_PortalGlow toned down (EmissiveStrength 4 -&gt; 1.6, deeper violet) so it no longer blooms to white.</t>
         </is>
       </c>
     </row>
@@ -3984,12 +4019,12 @@
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>Rendered from the new 3D models in a Blender icon studio</t>
+          <t>Rendered from the game's own models in a Blender icon studio (wave4_icons.py)</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Materials rebuilt from the Unreal MIs (Import/UI/icon_materials.json)</t>
         </is>
       </c>
       <c r="I60" s="1" t="inlineStr">
@@ -4004,7 +4039,12 @@
       </c>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L60" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5): 30 icons, 128 px with outline and shadow (wave4_icon_finish.py): every item in items.json. 22 re-rendered from the weapon/shield glb and MetaHuman armour FBX (same file names, so items.json and the web editor pick them up); 8 new (dagger_iron, totem_bone, ring_strength, ring_wisdom, potion_health, potion_mana, rat_tail, gold_coin, modelled in the studio) and set as inventoryIcon in items.json. The other 46 1.0 icons (32 px pixel art) belong to no current item and have no model; left as they are. Imported by import_ui_icons.py (bilinear + mips for 128 px, nearest for 32 px).</t>
         </is>
       </c>
     </row>
@@ -4041,12 +4081,12 @@
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>Blender-rendered emblems + painted frames</t>
+          <t>Procedural: signed-distance emblems shaded as raised metal (martial) or glowing light (spells) (wave4_skill_icons.py)</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Background washed in each skill's iconColor</t>
         </is>
       </c>
       <c r="I61" s="1" t="inlineStr">
@@ -4061,7 +4101,12 @@
       </c>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5): 41 icons, one per skill in skills.json, in Import/UI/Icons/Skills/&lt;id&gt;.png -&gt; /Game/Valhalla/UI/Icons/Skills. The action bar and skills pane show them; a skill without one keeps the generated code tile.</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4143,12 @@
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>Blender-rendered / procedural 2D</t>
+          <t>Procedural 2D (wave4_ui_frames.py)</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>CC0 materials</t>
+          <t>CC0 Leather (panel interior) + bronze / iron bevels</t>
         </is>
       </c>
       <c r="I62" s="1" t="inlineStr">
@@ -4118,12 +4163,12 @@
       </c>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
         <is>
-          <t>Pairs with B-07</t>
+          <t>Done 2026-09-24 (Opus 5.5): Nine-slice T_UI_Panel (leather in bronze trim, corner studs), T_UI_Slot (bronze rim, dark well), T_UI_Button, T_UI_BarFrame (iron), T_UI_BarFill (gloss ramp tinted by the bar colour) -&gt; /Game/Valhalla/UI/Frames. Applied to the current C++ HUD (MakePanel, MakeCell, MakeButton, MakeBar, combat log); B-07 can reuse them in a Widget Blueprint.  (Earlier note: Pairs with B-07)</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4329,7 @@
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
@@ -4304,12 +4349,12 @@
       </c>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
-          <t>NWN staple</t>
+          <t>NWN staple. Done 2026-09-24 (Opus 5.5, wave5_kit.py Tavern): 64 cm wall, window and corner, 128 cm door, a 3.6 m two-storey build (stone ground floor, jettied timber-and-plaster upper floor), 128 x 128 slate gable roof, chimney, hanging sign, plank floor. In /Game/Valhalla/Environment/Tavern. Poly Haven SlateRoof, OakPlanks, DarkPlanks. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4391,7 @@
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
@@ -4366,7 +4411,12 @@
       </c>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L66" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py Temple): 2.4 m limestone wall and pilaster wall, fluted marble column, altar with candles and a gilt sun disc, steps, mosaic floor, brazier, a hooded statue. Braziers and altar candles burn with the animated M_ValhallaFire and get a flickering light from fire_lights.py. Poly Haven TempleStone, Marble, TempleFloor. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4453,7 @@
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
@@ -4423,7 +4473,12 @@
       </c>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L67" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py Keep): 50 cm curtain walls in 1.28 m modules (plain and arrow slit), corner pier, round tower (2.16 m across, 4.8 m tall), gatehouse with a raised portcullis, banner. The gate uses its own triangles for collision, so players walk through the open arch (capsule-tested); it has no closed state yet. Outside faces +Y. Poly Haven KeepStone. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4515,7 @@
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: modular + broken variants</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
@@ -4480,7 +4535,12 @@
       </c>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py Ruins): block-laid broken walls (ragged tops, every block supported), corner, low wall, snapped and fallen columns, half arch (walk-through), broken statue, rubble. Poly Haven RuinStone, MossyRock. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4577,7 @@
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
@@ -4537,7 +4597,12 @@
       </c>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py River): humped stone bridge (3.84 m, 80 cm between the parapets), plank footbridge, river-bank edge strip and corner, reeds, stepping stones. Both bridges use their own triangles for collision and are walkable (capsule-tested). Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4639,7 @@
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural rock modular</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
@@ -4594,12 +4659,12 @@
       </c>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
         <is>
-          <t>Needed for B-06</t>
+          <t>Needed for B-06. Done 2026-09-24 (Opus 5.5, wave5_kit.py Cave): ledged rock walls 1.28 x 0.64 x 2.4 m and 1.4 m, pillar to hide joints and turn corners, a ceiling lip that overhangs 0.9 m (no full roof, for the top-down camera), floor tile, stalagmites, stalactites, glowing crystals, rubble. Poly Haven CaveRock, CaveFloor. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4758,7 @@
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: models</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
@@ -4713,7 +4778,12 @@
       </c>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py Interior): bar counter, table, chair, bench, bed, shelf, books, candle, chest, keg, fireplace, table clutter. The fireplace and candle burn with the animated M_ValhallaFire and get a flickering light from fire_lights.py. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4820,7 @@
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: models</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
@@ -4770,12 +4840,12 @@
       </c>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="L73" s="1" t="inlineStr">
         <is>
-          <t>EQ-style camps</t>
+          <t>EQ-style camps. Done 2026-09-24 (Opus 5.5, wave5_kit.py Camp): A-frame and bell tents, campfire, cooking fire (tripod and pot), bedroll, weapon rack, log seat, supply pile. Fires: animated M_ValhallaFire flames (rising noise, no shadow, no collision) plus a flickering PointLight per fire from fire_lights.add_all(). Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4882,7 @@
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: procedural foliage</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
@@ -4832,7 +4902,12 @@
       </c>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py Foliage): two bushes, grass tuft, two flower patches, fern, dead tree, stump, fallen log. Card materials (GrassTuft, Reeds, Fern, FlowersA/B, procedural, wave5_foliage_textures.py) on M_ValhallaFoliage; cards have no collision. No wind yet. Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4944,7 @@
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>Opus + Blender MCP: models</t>
+          <t>Opus 5.5 + Blender MCP: procedural (wave5_kit.py)</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
@@ -4889,7 +4964,12 @@
       </c>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t>Done 2026-09-24 (Opus 5.5, wave5_kit.py DesertVariety): half-buried ribcage and bones, horned skull, sandstone ruin wall and column, striped nomad awning with rug and cushions, pottery (amphorae, urn, shards). Review level /Game/Valhalla/Maps/Dev/L_ArtReview_Wave5.</t>
         </is>
       </c>
     </row>
